--- a/ClinicalDemogData_COFL.xlsx
+++ b/ClinicalDemogData_COFL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacquesleooscar/Documents/Education/ETHZ/Curriculum/Semester04/04MasterThesis/LTMM_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708D62C3-0F45-EB44-ACF9-3FEC85C8617A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF94A696-234F-AD4B-84C4-FA3249AA509F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="8" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="146">
   <si>
     <t>#</t>
   </si>
@@ -308,9 +308,6 @@
   </si>
   <si>
     <t>CO-039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N/A </t>
   </si>
   <si>
     <t>CO-042</t>
@@ -933,13 +930,13 @@
         <v>74</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>1</v>
@@ -996,22 +993,22 @@
         <v>9</v>
       </c>
       <c r="X1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="Y1" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="Z1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
@@ -1143,9 +1140,7 @@
       <c r="M3" s="3">
         <v>97.72</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>94</v>
-      </c>
+      <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>26</v>
       </c>
@@ -4473,7 +4468,7 @@
     </row>
     <row r="41" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B41" s="6">
         <v>41078</v>
@@ -4562,7 +4557,7 @@
     </row>
     <row r="42" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="6">
         <v>41093</v>
@@ -4647,7 +4642,7 @@
     </row>
     <row r="43" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B43" s="6">
         <v>41094</v>
@@ -4736,7 +4731,7 @@
     </row>
     <row r="44" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" s="6">
         <v>41102</v>
@@ -4825,7 +4820,7 @@
     </row>
     <row r="45" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B45" s="6">
         <v>41065</v>
@@ -4950,13 +4945,13 @@
         <v>74</v>
       </c>
       <c r="C1" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>104</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>1</v>
@@ -5013,22 +5008,22 @@
         <v>9</v>
       </c>
       <c r="X1" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y1" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="Y1" s="8" t="s">
-        <v>109</v>
-      </c>
       <c r="Z1" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="AA1" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="8" t="s">
+      <c r="AB1" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="8" t="s">
+      <c r="AC1" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="39" customHeight="1" x14ac:dyDescent="0.15">
@@ -7795,7 +7790,7 @@
     </row>
     <row r="34" spans="1:29" ht="38.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B34" s="6">
         <v>41094</v>
@@ -7904,43 +7899,43 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" t="s">
         <v>110</v>
-      </c>
-      <c r="B1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16" x14ac:dyDescent="0.15">
       <c r="A2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B2" t="s">
         <v>130</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>131</v>
-      </c>
-      <c r="C2" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -7948,7 +7943,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -7956,7 +7951,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -7964,7 +7959,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -7972,10 +7967,10 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>135</v>
+      </c>
+      <c r="C8" t="s">
         <v>136</v>
-      </c>
-      <c r="C8" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -7983,10 +7978,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
         <v>122</v>
-      </c>
-      <c r="C9" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -7994,10 +7989,10 @@
         <v>78</v>
       </c>
       <c r="B10" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" t="s">
         <v>140</v>
-      </c>
-      <c r="C10" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -8005,10 +8000,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>142</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8016,10 +8011,10 @@
         <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8027,10 +8022,10 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" t="s">
         <v>124</v>
-      </c>
-      <c r="C13" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8038,10 +8033,10 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" t="s">
         <v>128</v>
-      </c>
-      <c r="C14" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8049,10 +8044,10 @@
         <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8060,10 +8055,10 @@
         <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8071,10 +8066,10 @@
         <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8082,10 +8077,10 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8093,10 +8088,10 @@
         <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8104,10 +8099,10 @@
         <v>66</v>
       </c>
       <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
         <v>112</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.15">
@@ -8115,32 +8110,32 @@
         <v>9</v>
       </c>
       <c r="B21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" t="s">
         <v>112</v>
-      </c>
-      <c r="C21" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.15">
       <c r="A22" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" t="s">
         <v>144</v>
-      </c>
-      <c r="C22" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/ClinicalDemogData_COFL.xlsx
+++ b/ClinicalDemogData_COFL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacquesleooscar/Documents/Education/ETHZ/Curriculum/Semester04/04MasterThesis/LTMM_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF94A696-234F-AD4B-84C4-FA3249AA509F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B17CAA-8A1E-F844-8930-9EFA8C27890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="8" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="147">
   <si>
     <t>#</t>
   </si>
@@ -464,6 +464,9 @@
   </si>
   <si>
     <t>Walking while serially subtracting 3 seconds from a predefined 3-digit number arbitrarily determined by the clinician.</t>
+  </si>
+  <si>
+    <t>Year Fall</t>
   </si>
 </sst>
 </file>
@@ -942,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>11</v>
@@ -4957,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>2</v>
+        <v>146</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>11</v>

--- a/ClinicalDemogData_COFL.xlsx
+++ b/ClinicalDemogData_COFL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacquesleooscar/Documents/Education/ETHZ/Curriculum/Semester04/04MasterThesis/LTMM_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B17CAA-8A1E-F844-8930-9EFA8C27890D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31D9EB0-2441-964E-960A-CD67261178E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="8" r:id="rId1"/>

--- a/ClinicalDemogData_COFL.xlsx
+++ b/ClinicalDemogData_COFL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jacquesleooscar/Documents/Education/ETHZ/Curriculum/Semester04/04MasterThesis/LTMM_Analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31D9EB0-2441-964E-960A-CD67261178E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D518AAA5-20DD-A243-8A1A-717C55752CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" tabRatio="263" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Controls" sheetId="8" r:id="rId1"/>
@@ -4927,7 +4927,7 @@
     <col min="1" max="1" width="16.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="7" customWidth="1"/>
     <col min="3" max="4" width="16.83203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16" width="16.83203125" style="1" customWidth="1"/>
     <col min="17" max="17" width="19.33203125" style="1" customWidth="1"/>
     <col min="18" max="19" width="16.83203125" style="1" customWidth="1"/>
